--- a/Run_Log/1/student/AnhDThe187386/TC4/GradeDetail.xlsx
+++ b/Run_Log/1/student/AnhDThe187386/TC4/GradeDetail.xlsx
@@ -158,10 +158,10 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
+    <x:t>SYN_SENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASS</x:t>
   </x:si>
   <x:si>
     <x:t>SYN, ACK</x:t>
@@ -170,22 +170,58 @@
     <x:t>Server responding (SYN-ACK)</x:t>
   </x:si>
   <x:si>
+    <x:t>SYN-ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYN_RECEIVED</x:t>
+  </x:si>
+  <x:si>
     <x:t>ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Connection established</x:t>
   </x:si>
   <x:si>
+    <x:t>ESTABLISHED</x:t>
+  </x:si>
+  <x:si>
     <x:t>PSH, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Data transfer in progress</x:t>
   </x:si>
   <x:si>
+    <x:t>PSH-ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4 bytes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>160 bytes</x:t>
+  </x:si>
+  <x:si>
     <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN-ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN_WAIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARTIAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>115 bytes</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -212,7 +248,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -221,7 +257,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFF00"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -244,7 +290,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -254,8 +300,14 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -265,6 +317,14 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -891,11 +951,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R12"/>
+  <x:dimension ref="A1:R41"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -904,8 +964,8 @@
     <x:col min="8" max="8" width="4.996339" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14.139196" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1002,25 +1062,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q2" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P2" s="0">
+        <x:v>33238</x:v>
+      </x:c>
+      <x:c r="Q2" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>47</x:v>
@@ -1058,25 +1118,25 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q3" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P3" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q3" s="0">
+        <x:v>33238</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>47</x:v>
@@ -1099,10 +1159,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
@@ -1114,25 +1174,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P4" s="0">
+        <x:v>33238</x:v>
+      </x:c>
+      <x:c r="Q4" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>47</x:v>
@@ -1155,10 +1215,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
@@ -1170,25 +1230,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="P5" s="0">
+        <x:v>33238</x:v>
+      </x:c>
+      <x:c r="Q5" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>47</x:v>
@@ -1211,10 +1271,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
@@ -1226,25 +1286,25 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q6" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P6" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q6" s="0">
+        <x:v>33238</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>47</x:v>
@@ -1267,10 +1327,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
@@ -1282,25 +1342,25 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="P7" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q7" s="0">
+        <x:v>33238</x:v>
       </x:c>
       <x:c r="R7" s="2" t="s">
         <x:v>47</x:v>
@@ -1323,10 +1383,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
@@ -1338,25 +1398,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q8" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P8" s="0">
+        <x:v>33238</x:v>
+      </x:c>
+      <x:c r="Q8" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R8" s="2" t="s">
         <x:v>47</x:v>
@@ -1379,10 +1439,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
@@ -1394,28 +1454,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R9" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="P9" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q9" s="0">
+        <x:v>33238</x:v>
+      </x:c>
+      <x:c r="R9" s="3" t="s">
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1435,10 +1495,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
@@ -1450,25 +1510,25 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q10" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P10" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q10" s="0">
+        <x:v>33238</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>47</x:v>
@@ -1491,10 +1551,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>17</x:v>
@@ -1506,28 +1566,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R11" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="P11" s="0">
+        <x:v>33238</x:v>
+      </x:c>
+      <x:c r="Q11" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R11" s="3" t="s">
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:18">
@@ -1547,10 +1607,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>17</x:v>
@@ -1562,28 +1622,1652 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q12" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P12" s="0">
+        <x:v>39378</x:v>
+      </x:c>
+      <x:c r="Q12" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R12" s="2" t="s">
         <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:18">
+      <x:c r="A13" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P13" s="0">
+        <x:v>39378</x:v>
+      </x:c>
+      <x:c r="Q13" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R13" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:18">
+      <x:c r="A14" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K14" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="M14" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P14" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q14" s="0">
+        <x:v>39378</x:v>
+      </x:c>
+      <x:c r="R14" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:18">
+      <x:c r="A15" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K15" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L15" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M15" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N15" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O15" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="P15" s="0">
+        <x:v>39378</x:v>
+      </x:c>
+      <x:c r="Q15" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R15" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:18">
+      <x:c r="A16" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K16" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L16" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M16" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N16" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P16" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q16" s="0">
+        <x:v>39378</x:v>
+      </x:c>
+      <x:c r="R16" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:18">
+      <x:c r="A17" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K17" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L17" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M17" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N17" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O17" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="P17" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q17" s="0">
+        <x:v>39378</x:v>
+      </x:c>
+      <x:c r="R17" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:18">
+      <x:c r="A18" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K18" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M18" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N18" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P18" s="0">
+        <x:v>39378</x:v>
+      </x:c>
+      <x:c r="Q18" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R18" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:18">
+      <x:c r="A19" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K19" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L19" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M19" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N19" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P19" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q19" s="0">
+        <x:v>39378</x:v>
+      </x:c>
+      <x:c r="R19" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:18">
+      <x:c r="A20" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K20" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L20" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M20" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N20" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P20" s="0">
+        <x:v>39378</x:v>
+      </x:c>
+      <x:c r="Q20" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R20" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:18">
+      <x:c r="A21" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K21" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L21" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M21" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N21" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P21" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q21" s="0">
+        <x:v>39378</x:v>
+      </x:c>
+      <x:c r="R21" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:18">
+      <x:c r="A22" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K22" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L22" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="M22" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N22" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P22" s="0">
+        <x:v>37172</x:v>
+      </x:c>
+      <x:c r="Q22" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R22" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:18">
+      <x:c r="A23" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K23" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L23" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="M23" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N23" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P23" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q23" s="0">
+        <x:v>37172</x:v>
+      </x:c>
+      <x:c r="R23" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:18">
+      <x:c r="A24" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K24" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L24" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M24" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N24" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P24" s="0">
+        <x:v>37172</x:v>
+      </x:c>
+      <x:c r="Q24" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R24" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:18">
+      <x:c r="A25" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K25" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L25" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M25" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N25" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O25" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="P25" s="0">
+        <x:v>37172</x:v>
+      </x:c>
+      <x:c r="Q25" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R25" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:18">
+      <x:c r="A26" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K26" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L26" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M26" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N26" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P26" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q26" s="0">
+        <x:v>37172</x:v>
+      </x:c>
+      <x:c r="R26" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:18">
+      <x:c r="A27" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K27" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L27" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M27" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N27" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O27" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="P27" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q27" s="0">
+        <x:v>37172</x:v>
+      </x:c>
+      <x:c r="R27" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:18">
+      <x:c r="A28" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K28" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L28" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M28" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N28" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P28" s="0">
+        <x:v>37172</x:v>
+      </x:c>
+      <x:c r="Q28" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R28" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:18">
+      <x:c r="A29" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K29" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L29" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M29" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N29" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P29" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q29" s="0">
+        <x:v>37172</x:v>
+      </x:c>
+      <x:c r="R29" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:18">
+      <x:c r="A30" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K30" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L30" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M30" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N30" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P30" s="0">
+        <x:v>37172</x:v>
+      </x:c>
+      <x:c r="Q30" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R30" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:18">
+      <x:c r="A31" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K31" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L31" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M31" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N31" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P31" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q31" s="0">
+        <x:v>37172</x:v>
+      </x:c>
+      <x:c r="R31" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:18">
+      <x:c r="A32" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K32" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L32" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="M32" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N32" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P32" s="0">
+        <x:v>43260</x:v>
+      </x:c>
+      <x:c r="Q32" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R32" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:18">
+      <x:c r="A33" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K33" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L33" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="M33" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N33" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P33" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q33" s="0">
+        <x:v>43260</x:v>
+      </x:c>
+      <x:c r="R33" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:18">
+      <x:c r="A34" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K34" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L34" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M34" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N34" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P34" s="0">
+        <x:v>43260</x:v>
+      </x:c>
+      <x:c r="Q34" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R34" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:18">
+      <x:c r="A35" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J35" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K35" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L35" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M35" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N35" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O35" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="P35" s="0">
+        <x:v>43260</x:v>
+      </x:c>
+      <x:c r="Q35" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R35" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:18">
+      <x:c r="A36" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K36" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L36" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M36" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N36" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O36" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P36" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q36" s="0">
+        <x:v>43260</x:v>
+      </x:c>
+      <x:c r="R36" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:18">
+      <x:c r="A37" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J37" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K37" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L37" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M37" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N37" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O37" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="P37" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q37" s="0">
+        <x:v>43260</x:v>
+      </x:c>
+      <x:c r="R37" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:18">
+      <x:c r="A38" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K38" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L38" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M38" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N38" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O38" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P38" s="0">
+        <x:v>43260</x:v>
+      </x:c>
+      <x:c r="Q38" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R38" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:18">
+      <x:c r="A39" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K39" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L39" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M39" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N39" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O39" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P39" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q39" s="0">
+        <x:v>43260</x:v>
+      </x:c>
+      <x:c r="R39" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:18">
+      <x:c r="A40" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K40" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L40" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M40" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N40" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O40" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P40" s="0">
+        <x:v>43260</x:v>
+      </x:c>
+      <x:c r="Q40" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R40" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:18">
+      <x:c r="A41" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K41" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L41" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M41" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N41" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O41" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P41" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q41" s="0">
+        <x:v>43260</x:v>
+      </x:c>
+      <x:c r="R41" s="4" t="s">
+        <x:v>66</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
